--- a/data/timisoara/rca_analysis.xlsx
+++ b/data/timisoara/rca_analysis.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -874,6 +874,262 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:44</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Sanding_System</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Kumlama Kontrol ünitesi</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:34</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Traction_Converter</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Tahrik Konvertörü Sis.  Batary charger</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>bater</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:35</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>TCMS</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>TCMS CAN/Ethernet geçiş modülü</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:39</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Pantograf</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Pantograf Esnek Halat</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:44</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Traction_Converter</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Fren Rezistörü</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:43</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Driver_HVAC_System</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>HVAC Sürücü Evaporatör  Fan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:29</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Brake_System</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Fren Akümülatör</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:30</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:44</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Sanding_System</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Kumlama Kontrol ünitesi</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
